--- a/product_surveys/005_photography_equipment_survey--product_surveys.xlsx
+++ b/product_surveys/005_photography_equipment_survey--product_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -849,8 +849,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="33" customWidth="1" min="2" max="2"/>
-    <col width="33" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="2" max="2"/>
+    <col width="20" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -878,12 +878,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'label':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'label': 'Very Satisfied'}</t>
+          <t>Very Satisfied</t>
         </is>
       </c>
     </row>
@@ -895,12 +895,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Satisfied'}</t>
+          <t>Somewhat Satisfied</t>
         </is>
       </c>
     </row>
@@ -912,12 +912,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'label':_'not_satisfied'}</t>
+          <t>not_satisfied</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'label': 'Not Satisfied'}</t>
+          <t>Not Satisfied</t>
         </is>
       </c>
     </row>
@@ -929,12 +929,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -946,12 +946,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -963,12 +963,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely'}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -980,12 +980,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'label': 'Not at All Likely'}</t>
+          <t>Not at All Likely</t>
         </is>
       </c>
     </row>
@@ -997,12 +997,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'label':_'camera'}</t>
+          <t>camera</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'label': 'Camera'}</t>
+          <t>Camera</t>
         </is>
       </c>
     </row>
@@ -1014,12 +1014,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'label':_'lens'}</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'label': 'Lens'}</t>
+          <t>Lens</t>
         </is>
       </c>
     </row>
@@ -1031,12 +1031,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'label':_'tripod'}</t>
+          <t>tripod</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'label': 'Tripod'}</t>
+          <t>Tripod</t>
         </is>
       </c>
     </row>
@@ -1048,12 +1048,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'label':_'flash'}</t>
+          <t>flash</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'label': 'Flash'}</t>
+          <t>Flash</t>
         </is>
       </c>
     </row>
@@ -1065,12 +1065,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1082,12 +1082,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'label':_'camera'}</t>
+          <t>camera</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'label': 'Camera'}</t>
+          <t>Camera</t>
         </is>
       </c>
     </row>
@@ -1099,12 +1099,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'label':_'lens'}</t>
+          <t>lens</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'label': 'Lens'}</t>
+          <t>Lens</t>
         </is>
       </c>
     </row>
@@ -1116,12 +1116,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'label':_'tripod'}</t>
+          <t>tripod</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'label': 'Tripod'}</t>
+          <t>Tripod</t>
         </is>
       </c>
     </row>
@@ -1133,12 +1133,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'label':_'flash'}</t>
+          <t>flash</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'label': 'Flash'}</t>
+          <t>Flash</t>
         </is>
       </c>
     </row>
@@ -1150,12 +1150,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'label':_'other'}</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'label': 'Other'}</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1167,12 +1167,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'label':_'very_good'}</t>
+          <t>very_good</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'label': 'Very Good'}</t>
+          <t>Very Good</t>
         </is>
       </c>
     </row>
@@ -1184,12 +1184,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'label':_'good'}</t>
+          <t>good</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'label': 'Good'}</t>
+          <t>Good</t>
         </is>
       </c>
     </row>
@@ -1201,12 +1201,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'label':_'fair'}</t>
+          <t>fair</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'label': 'Fair'}</t>
+          <t>Fair</t>
         </is>
       </c>
     </row>
@@ -1218,12 +1218,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'label':_'not_good'}</t>
+          <t>not_good</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'label': 'Not Good'}</t>
+          <t>Not Good</t>
         </is>
       </c>
     </row>
@@ -1235,12 +1235,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'label':_'reasonable'}</t>
+          <t>reasonable</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'label': 'Reasonable'}</t>
+          <t>Reasonable</t>
         </is>
       </c>
     </row>
@@ -1252,12 +1252,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'label':_'too_high'}</t>
+          <t>too_high</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'label': 'Too High'}</t>
+          <t>Too High</t>
         </is>
       </c>
     </row>
@@ -1269,12 +1269,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'label':_'not_too_high'}</t>
+          <t>not_too_high</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'label': 'Not Too High'}</t>
+          <t>Not Too High</t>
         </is>
       </c>
     </row>
@@ -1286,12 +1286,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1303,12 +1303,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1320,12 +1320,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely'}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1337,12 +1337,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'label': 'Not at All Likely'}</t>
+          <t>Not at All Likely</t>
         </is>
       </c>
     </row>
@@ -1354,12 +1354,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1371,12 +1371,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1388,12 +1388,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely'}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1405,12 +1405,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'label': 'Not at All Likely'}</t>
+          <t>Not at All Likely</t>
         </is>
       </c>
     </row>
@@ -1422,12 +1422,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'label':_'very_likely'}</t>
+          <t>very_likely</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'label': 'Very Likely'}</t>
+          <t>Very Likely</t>
         </is>
       </c>
     </row>
@@ -1439,12 +1439,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'label':_'somewhat_likely'}</t>
+          <t>somewhat_likely</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'label': 'Somewhat Likely'}</t>
+          <t>Somewhat Likely</t>
         </is>
       </c>
     </row>
@@ -1456,12 +1456,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'label':_'not_likely'}</t>
+          <t>not_likely</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'label': 'Not Likely'}</t>
+          <t>Not Likely</t>
         </is>
       </c>
     </row>
@@ -1473,12 +1473,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'label':_'not_at_all_likely'}</t>
+          <t>not_at_all_likely</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'label': 'Not at All Likely'}</t>
+          <t>Not at All Likely</t>
         </is>
       </c>
     </row>
